--- a/docs/cmdb/shieldtest-cmdb.xlsx
+++ b/docs/cmdb/shieldtest-cmdb.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VPS Inventory" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Network &amp; Firewall" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roles &amp; Services" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repositories &amp; CICD" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Endpoints" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Environment Variables" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secrets Registry" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Engagement" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="VPS Inventory" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Network &amp; Firewall" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Roles &amp; Services" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Repositories &amp; CICD" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Endpoints" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Environment Variables" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Secrets Registry" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Engagement" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Change Log" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -622,7 +622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -798,13 +798,47 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr"/>
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>PENDING: VPS 2 lab runner (host-lab.sh) + scrubber hook PROTECTION_METRICS_URL + full pretest-cra-l7 suite.</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr"/>
+          <t>Admin SSH access established from workstation via dedicated key ~/.ssh/shieldtest_vps (ed25519, authorized_keys on VPS1+VPS2). VPS1 /health=ok (build 184), VPS2 verified.</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Claude/abdelha</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>VPS 2 lab runner LIVE: systemd shieldtest-lab-runner active (RUNNER_ID=vm32046), repo /opt/shieldtest-lab @ c752a06. Reaches VPS1 API via SSH tunnel (ssh -L 127.0.0.1:8080 -&gt; VPS1:8080, key /root/.ssh/vps1_tunnel). Claimed+handled class-C job udp_dns_reflection -&gt; UNMITIGATED_BASELINE (bounded dns burst, 720 pkts, within caps).</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Claude/abdelha</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr"/>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>PENDING: scrubber hook PROTECTION_METRICS_URL (VPS1 protection=false) + full pretest-cra-l7 suite. Reminder: rotate the 3 generated secrets (transcript-exposed).</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2636,7 +2670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2920,44 +2954,108 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
+          <t>Admin SSH key: shieldtest_vps</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>workstation -&gt; VPS1+VPS2 admin login</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>authorized_keys on both VPS</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Workstation ~/.ssh (no passphrase)</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>ssh-keygen ed25519</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>active (2026-09-09)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Tunnel SSH key: vps1_tunnel</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>VPS2 -&gt; VPS1 API tunnel (ssh -L 8080)</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>VPS2 /root/.ssh; authorized on VPS1</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>VPS2 filesystem</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>ssh-keygen</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
           <t>PROTECTION_METRICS_URL</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>scrubber hook endpoint</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>VPS 1 env</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>Password manager / infra note</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>WEDOS scrubber</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t>PENDING — not yet wired</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Reminder: the three generated secrets were pasted into a chat transcript on 2026-09-09; rotate if that transcript is considered exposed.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>After first SSH login on each VPS: change root password, install an admin SSH key, disable password auth.</t>
         </is>

--- a/docs/cmdb/shieldtest-cmdb.xlsx
+++ b/docs/cmdb/shieldtest-cmdb.xlsx
@@ -622,7 +622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -832,13 +832,115 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr"/>
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>PENDING: scrubber hook PROTECTION_METRICS_URL (VPS1 protection=false) + full pretest-cra-l7 suite. Reminder: rotate the 3 generated secrets (transcript-exposed).</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr"/>
+          <t>CD FIXED: vps1 self-hosted runner registered (label vps1), ac02 removed; .git repropriated to shieldtest (root-owned .git broke the runner). Deploy workflow green on merge to main.</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Protection hook WIRED: PROTECTION_METRICS_URL=http://127.0.0.1:8080/api/protection/lab-metrics (lab-scrubber adapter, source wedos-lab-scrubber) -&gt; /health protection=true. 404 when no lab mitigation measured -&gt; clean fall-back to estimate.</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>MAJOR BUG fixed: multi-phase (wave/ramp) runs hung indefinitely vs bank.cz (617s for 180s cap) — undici leaves fetches queued on an exhausted keep-alive pool, abort ignored. Fix: probe wall-clock deadline + engine hard backstop (cap+15s). PRs #14/#15.</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>All 19 campaign templates validated end-to-end vs bank.cz: every step COMPLETED (protection engaged -&gt; 4xx/tarpit, WRS ~97 A+). Orchestrated via 4 dedicated DB test accounts claude-{engineer,officer,ciso,viewer}@wedos (pw in /root/claude-test-accounts.json, root-only).</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Reports made faithful under throttling (configured-&gt;effective load, protection-absorbed callout, failure split) PR #16. Observability added: /metrics runtime (http/runs/hard-stop/event-loop lag) + run.start/run.settled structured logs, PR #17.</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Monitoring stack prepared on VPS 2 (deploy/provision/host-monitoring.sh: node_exporter+Prometheus+Grafana, loopback, scrapes VPS1 /metrics via existing tunnel). Awaiting run (apt install).</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr"/>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>PENDING: run host-monitoring.sh on VPS2; rotate the 3 generated secrets (transcript-exposed); ufw fail-closed VPS2 (issue #12); real WEDOS scrubber endpoint for measured TTD/TTM.</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
